--- a/artfynd/A 16027-2024 artfynd.xlsx
+++ b/artfynd/A 16027-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>117648164</v>
+        <v>117648439</v>
       </c>
       <c r="B2" t="n">
-        <v>5166</v>
+        <v>90660</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,32 +687,30 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100526</v>
+        <v>1588</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Violmussling</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Trichaptum laricinum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(P.Karst.) Ryvarden</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -720,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>865061</v>
+        <v>865122</v>
       </c>
       <c r="R2" t="n">
-        <v>7413685</v>
+        <v>7413589</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -783,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>117648439</v>
+        <v>117648238</v>
       </c>
       <c r="B3" t="n">
-        <v>90660</v>
+        <v>78217</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1588</v>
+        <v>228912</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Violmussling</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Trichaptum laricinum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Ryvarden</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -826,10 +824,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>865122</v>
+        <v>865111</v>
       </c>
       <c r="R3" t="n">
-        <v>7413589</v>
+        <v>7413689</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -1101,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>117648326</v>
+        <v>117648309</v>
       </c>
       <c r="B6" t="n">
-        <v>79590</v>
+        <v>97857</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1117,26 +1115,27 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6462</v>
+        <v>221952</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1144,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>865063</v>
+        <v>865069</v>
       </c>
       <c r="R6" t="n">
-        <v>7413681</v>
+        <v>7413696</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1207,10 +1206,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>117648309</v>
+        <v>117648326</v>
       </c>
       <c r="B7" t="n">
-        <v>97857</v>
+        <v>79590</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1223,27 +1222,26 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221952</v>
+        <v>6462</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1251,10 +1249,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>865069</v>
+        <v>865063</v>
       </c>
       <c r="R7" t="n">
-        <v>7413696</v>
+        <v>7413681</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1314,10 +1312,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>117648238</v>
+        <v>117648164</v>
       </c>
       <c r="B8" t="n">
-        <v>78217</v>
+        <v>5166</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1326,30 +1324,32 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>228912</v>
+        <v>100526</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>865111</v>
+        <v>865061</v>
       </c>
       <c r="R8" t="n">
-        <v>7413689</v>
+        <v>7413685</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>

--- a/artfynd/A 16027-2024 artfynd.xlsx
+++ b/artfynd/A 16027-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>117648439</v>
+        <v>117648326</v>
       </c>
       <c r="B2" t="n">
-        <v>90660</v>
+        <v>79592</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1588</v>
+        <v>6462</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Violmussling</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Trichaptum laricinum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Ryvarden</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -718,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>865122</v>
+        <v>865063</v>
       </c>
       <c r="R2" t="n">
-        <v>7413589</v>
+        <v>7413681</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>117648238</v>
+        <v>117648139</v>
       </c>
       <c r="B3" t="n">
-        <v>78217</v>
+        <v>5166</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,30 +793,32 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>228912</v>
+        <v>100526</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -824,10 +826,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>865111</v>
+        <v>865083</v>
       </c>
       <c r="R3" t="n">
-        <v>7413689</v>
+        <v>7413675</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -887,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>117648291</v>
+        <v>117648193</v>
       </c>
       <c r="B4" t="n">
-        <v>57303</v>
+        <v>78219</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,27 +905,26 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -931,10 +932,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>865097</v>
+        <v>865120</v>
       </c>
       <c r="R4" t="n">
-        <v>7413709</v>
+        <v>7413576</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -975,6 +976,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -993,10 +995,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>117648193</v>
+        <v>117648164</v>
       </c>
       <c r="B5" t="n">
-        <v>78217</v>
+        <v>5166</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1005,30 +1007,32 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>228912</v>
+        <v>100526</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1036,10 +1040,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>865120</v>
+        <v>865061</v>
       </c>
       <c r="R5" t="n">
-        <v>7413576</v>
+        <v>7413685</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -1102,7 +1106,7 @@
         <v>117648309</v>
       </c>
       <c r="B6" t="n">
-        <v>97857</v>
+        <v>97859</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1206,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>117648326</v>
+        <v>117648291</v>
       </c>
       <c r="B7" t="n">
-        <v>79590</v>
+        <v>57304</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1218,30 +1222,31 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6462</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1249,10 +1254,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>865063</v>
+        <v>865097</v>
       </c>
       <c r="R7" t="n">
-        <v>7413681</v>
+        <v>7413709</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1293,7 +1298,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1312,10 +1316,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>117648164</v>
+        <v>117648439</v>
       </c>
       <c r="B8" t="n">
-        <v>5166</v>
+        <v>90662</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1324,32 +1328,30 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100526</v>
+        <v>1588</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Violmussling</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Trichaptum laricinum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(P.Karst.) Ryvarden</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1357,10 +1359,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>865061</v>
+        <v>865122</v>
       </c>
       <c r="R8" t="n">
-        <v>7413685</v>
+        <v>7413589</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1420,10 +1422,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>117648139</v>
+        <v>117648238</v>
       </c>
       <c r="B9" t="n">
-        <v>5166</v>
+        <v>78219</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1432,32 +1434,30 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100526</v>
+        <v>228912</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1465,10 +1465,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>865083</v>
+        <v>865111</v>
       </c>
       <c r="R9" t="n">
-        <v>7413675</v>
+        <v>7413689</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
